--- a/public/sample_uploads/investor_kpi_mappings_test_1.xlsx
+++ b/public/sample_uploads/investor_kpi_mappings_test_1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <workbookPr date1904="false"/>
   <sheets>
-    <sheet sheetId="1" name="InvestorKPIMapping" r:id="rId1"/>
+    <sheet name="InvestorKPIMapping" sheetId="1" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
   <numFmts count="2">
-    <numFmt formatCode="yyyy/mm/dd" numFmtId="100"/>
-    <numFmt formatCode="yyyy/mm/dd hh:mm:ss" numFmtId="101"/>
+    <numFmt numFmtId="100" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="101" formatCode="yyyy/mm/dd hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
       <name val="Arial"/>
+      <family val="1"/>
       <sz val="11"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -323,30 +323,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
   <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.5" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="13.200000000000001" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="29.700000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="12.100000000000001" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="19.8" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="19.8" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="13.200000000000001" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="19.8" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="15.400000000000002" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.200000000000003" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.200000000000001" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.700000000000003" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.100000000000001" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.700000000000003" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.200000000000001" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.400000000000002" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" customFormat="false">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Stakeholder</t>
@@ -417,8 +417,11 @@
           <t>Denomination</t>
         </is>
       </c>
+      <c r="O1" s="0" t="str">
+        <v>Fx Conversion</v>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14" customFormat="false">
       <c r="A2" s="0" t="inlineStr">
         <is>
           <t>MyFavStartup</t>
@@ -472,7 +475,7 @@
       </c>
       <c r="N2" s="0"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:14" customFormat="false">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>MyFavStartup</t>
@@ -526,7 +529,7 @@
       </c>
       <c r="N3" s="0"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" customFormat="false">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>MyFavStartup</t>
@@ -580,7 +583,7 @@
       </c>
       <c r="N4" s="0"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" customFormat="false">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>MyFavStartup</t>
@@ -636,8 +639,8 @@
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup/>
   <headerFooter/>
 </worksheet>
